--- a/data/trans_orig/IP19C09-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP19C09-Provincia-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4071</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3432</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>579</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4594</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15250</t>
+          <t>15547</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23086</t>
+          <t>23571</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41245</t>
+          <t>40767</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45268</t>
+          <t>45260</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4487</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54056</t>
+          <t>54096</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61714</t>
+          <t>61375</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>117710</t>
+          <t>118025</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>606</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>5526</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30442</t>
+          <t>30438</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34722</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>64699</t>
+          <t>64095</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69020</t>
+          <t>69021</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38288</t>
+          <t>38272</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>78985</t>
+          <t>79313</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4912</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4651</t>
+          <t>4568</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21279</t>
+          <t>21508</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44008</t>
+          <t>44091</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3668</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21672</t>
+          <t>22370</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25024</t>
+          <t>25063</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49169</t>
+          <t>49376</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4568</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5659</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>61629</t>
+          <t>61109</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>63461</t>
+          <t>63956</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>127822</t>
+          <t>127655</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2557</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>10277</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>78195</t>
+          <t>78197</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>65212</t>
+          <t>64986</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>72350</t>
+          <t>71856</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>144767</t>
+          <t>145457</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>152689</t>
+          <t>153085</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6609</t>
+          <t>6994</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17076</t>
+          <t>17441</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10510</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>22854</t>
+          <t>23692</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>340926</t>
+          <t>341599</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>348698</t>
+          <t>348994</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>344655</t>
+          <t>344290</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>355122</t>
+          <t>354737</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>689807</t>
+          <t>688969</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>702412</t>
+          <t>702151</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>4661</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26091</t>
+          <t>25341</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47892</t>
+          <t>46654</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>3684</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45181</t>
+          <t>45786</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52507</t>
+          <t>53341</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>101889</t>
+          <t>101897</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>719</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28894</t>
+          <t>28859</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34391</t>
+          <t>34260</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>65580</t>
+          <t>65326</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72196</t>
+          <t>72189</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>3683</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37544</t>
+          <t>37695</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>78589</t>
+          <t>77966</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4337</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21002</t>
+          <t>20589</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45027</t>
+          <t>45036</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>3473</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32381</t>
+          <t>32364</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>62445</t>
+          <t>63215</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>60616</t>
+          <t>60137</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>127436</t>
+          <t>127788</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>670</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6549</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>71751</t>
+          <t>71641</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>63538</t>
+          <t>64168</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69420</t>
+          <t>69417</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>137914</t>
+          <t>138079</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>144146</t>
+          <t>144546</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>2675</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11014</t>
+          <t>11731</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12290</t>
+          <t>12029</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7098</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>19184</t>
+          <t>19105</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>335439</t>
+          <t>334722</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>343937</t>
+          <t>343778</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>348197</t>
+          <t>348458</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>357450</t>
+          <t>357360</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>687756</t>
+          <t>687835</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>699842</t>
+          <t>699857</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4169</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24545</t>
+          <t>24821</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48796</t>
+          <t>48697</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>657</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46250</t>
+          <t>45849</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51138</t>
+          <t>51144</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>100953</t>
+          <t>101047</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>106479</t>
+          <t>106480</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28709</t>
+          <t>27899</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27019</t>
+          <t>26793</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57345</t>
+          <t>57365</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>792</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6563</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>686</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10192</t>
+          <t>10608</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37064</t>
+          <t>37008</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43069</t>
+          <t>42835</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42004</t>
+          <t>41642</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>48249</t>
+          <t>48256</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>82377</t>
+          <t>81961</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>90632</t>
+          <t>90752</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>4233</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11289</t>
+          <t>11685</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27441</t>
+          <t>27029</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36351</t>
+          <t>35763</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34180</t>
+          <t>34200</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>72188</t>
+          <t>71836</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>77402</t>
+          <t>77393</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>563</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6286</t>
+          <t>6204</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>8997</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>71854</t>
+          <t>71699</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>76301</t>
+          <t>76299</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>69883</t>
+          <t>69965</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>75542</t>
+          <t>75545</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>144532</t>
+          <t>144034</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>151106</t>
+          <t>151187</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4889</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14960</t>
+          <t>14753</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15423</t>
+          <t>15426</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>11418</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>25541</t>
+          <t>25186</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>332222</t>
+          <t>332429</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>342418</t>
+          <t>342293</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>340855</t>
+          <t>340852</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>351497</t>
+          <t>351586</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>677919</t>
+          <t>678274</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>691793</t>
+          <t>692042</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
